--- a/public/WoundCare_Competitor_Analysis.xlsx
+++ b/public/WoundCare_Competitor_Analysis.xlsx
@@ -7,13 +7,13 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Competitor Overview" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary by Category" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Key Insights" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1-to-1 Comparisons" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tender Products" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Company Directory" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Competitor Overview'!$A$1:$I$21</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Summary by Category'!$A$1:$G$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'1-to-1 Comparisons'!$A$1:$M$21</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -22,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -39,16 +39,8 @@
       <b val="1"/>
       <color rgb="00FF0000"/>
     </font>
-    <font>
-      <b val="1"/>
-      <sz val="14"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -63,8 +55,26 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00D6E4F0"/>
         <bgColor rgb="00D6E4F0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F2F2"/>
+        <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F0F4F8"/>
+        <bgColor rgb="00F0F4F8"/>
       </patternFill>
     </fill>
   </fills>
@@ -86,29 +96,28 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -475,64 +484,88 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:M21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="50" customWidth="1" min="9" max="9"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="6" max="6"/>
+    <col width="32" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="28" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="45" customWidth="1" min="12" max="12"/>
+    <col width="45" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Category #</t>
+          <t>Cat</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Product Category</t>
+          <t>Tender Product</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Your Tender Product (Spanish Name)</t>
+          <t>Tender Size</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>Qty</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Competitive Status</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Competitor Company</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Competitor Product Name</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Country / HQ</t>
-        </is>
-      </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>Competitor Product</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Match Type</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>Website</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>FDA Cleared?</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Key Differentiator / Notes</t>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>FDA Status</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>How It Compares to Tender</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Key Differences</t>
         </is>
       </c>
     </row>
@@ -547,78 +580,104 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Apósito a base de colágeno y alginato (4" x 4⅜")</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>3M / Solventum (formerly Systagenix)</t>
-        </is>
+          <t>10.2cm x 11.1cm (4" x 4⅜")</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>115200</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
+          <t>Competitive</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>3M / Solventum</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
           <t>FIBRACOL Plus</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>EXACT MATCH</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>solventum.com</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>Yes (K982597)</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>90% collagen / 10% calcium alginate. The original collagen-alginate combo. 4"x4-3/8" size matches tender exactly.</t>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>https://solventum.com</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>Yes — 510(k) K982597</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>90% collagen / 10% calcium alginate. 4"x4-3/8" size matches tender exactly.</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>Original collagen-alginate combo dressing. Benchmark product.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>Collagen-Alginate Wound Dressing</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr"/>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>Human BioSciences (HBS)</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>Medifil II / SkinTemp II</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr"/>
+      <c r="C3" s="2" t="inlineStr"/>
+      <c r="D3" s="2" t="inlineStr"/>
+      <c r="E3" s="2" t="inlineStr"/>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>Human BioSciences</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>Medifil II</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>CLOSE MATCH</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>humanbiosciences.com</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>https://humanbiosciences.com</t>
+        </is>
+      </c>
+      <c r="K3" s="4" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>Collagen wound dressings with alginate options.</t>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>100% type I bovine native collagen particles. Different format (particles vs sheet).</t>
+        </is>
+      </c>
+      <c r="M3" s="4" t="inlineStr">
+        <is>
+          <t>Collagen particles rather than sheet dressing — requires secondary dressing.</t>
         </is>
       </c>
     </row>
@@ -626,81 +685,97 @@
       <c r="A4" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Collagen-Alginate Wound Dressing</t>
-        </is>
-      </c>
+      <c r="B4" s="2" t="inlineStr"/>
       <c r="C4" s="2" t="inlineStr"/>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr"/>
+      <c r="E4" s="2" t="inlineStr"/>
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>Safe n' Simple</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>Simpurity Collagen Pad</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>CLOSE MATCH</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>safensimple.com</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>https://sns-medical.com</t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>4"x4" collagen pad, cost-effective alternative.</t>
+      <c r="L4" s="4" t="inlineStr">
+        <is>
+          <t>4"x4" collagen pad available. Full wound care line.</t>
+        </is>
+      </c>
+      <c r="M4" s="4" t="inlineStr">
+        <is>
+          <t>Collagen-only pad, no alginate component. Lower cost alternative.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>Collagen-Alginate Wound Dressing</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr"/>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr"/>
+      <c r="C5" s="2" t="inlineStr"/>
+      <c r="D5" s="2" t="inlineStr"/>
+      <c r="E5" s="2" t="inlineStr"/>
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>DermaRite Industries</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>DermaCol/Ag Collagen Dressings</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>DermaCol/Ag</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>CLOSE MATCH</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>dermarite.com</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>https://dermarite.com</t>
+        </is>
+      </c>
+      <c r="K5" s="4" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>Silver and non-silver collagen options.</t>
+      <c r="L5" s="4" t="inlineStr">
+        <is>
+          <t>Collagen + sodium alginate + CMC + EDTA matrix. Silver variant available.</t>
+        </is>
+      </c>
+      <c r="M5" s="4" t="inlineStr">
+        <is>
+          <t>Added CMC and EDTA beyond standard collagen-alginate.</t>
         </is>
       </c>
     </row>
@@ -708,85 +783,111 @@
       <c r="A6" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Collagen-Alginate Wound Dressing</t>
-        </is>
-      </c>
+      <c r="B6" s="2" t="inlineStr"/>
       <c r="C6" s="2" t="inlineStr"/>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr"/>
+      <c r="E6" s="2" t="inlineStr"/>
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>Foryou Medical (LUOFUCON)</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>Collagen Wound Dressing</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>ALTERNATIVE</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
         <is>
           <t>China</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>foryoumedical.com</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>Yes (510k)</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>Lower-cost manufacturer with FDA clearance.</t>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>https://en.foryoumedical.com</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="inlineStr">
+        <is>
+          <t>Yes — 510(k)</t>
+        </is>
+      </c>
+      <c r="L6" s="5" t="inlineStr">
+        <is>
+          <t>Chinese manufacturer with FDA-cleared collagen dressings.</t>
+        </is>
+      </c>
+      <c r="M6" s="5" t="inlineStr">
+        <is>
+          <t>Lower cost. May not have same LatAm distribution network.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>Nano-structured Hemicellulose Membrane &amp; Gel</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>Sistema de membrana y gel de hemicelulosa de nanoestructura (8cm x 8cm)</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Nano Hemicellulose Membrane &amp; Gel</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Membrane 8cm x 8cm, Gel 90ml</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>3600</v>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>SINGLE SOURCE</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>Genadyne Biotechnologies</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="G7" s="3" t="inlineStr">
         <is>
           <t>NanoGen Aktiv + NanoGen Aktigel</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>USA (NY)</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>genadyne.com</t>
-        </is>
-      </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
+          <t>EXACT MATCH — SOLE MANUFACTURER</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>USA (New York)</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>https://genadyne.com</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="I7" s="3" t="inlineStr">
-        <is>
-          <t>SOLE MANUFACTURER matching all specs. Plant stem cells, nanotechnology, positively charged, no silver. Distributed in LatAm by Promedon &amp; IGEA.</t>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>This IS the product described in the tender. Plant stem cells, nano-hemicellulose, positively charged, no silver.</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>Only manufacturer worldwide. Distributed in LatAm by Promedon &amp; IGEA.</t>
         </is>
       </c>
     </row>
@@ -796,83 +897,109 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Lyophilized 3D Open-Pore Collagen Matrix</t>
+          <t>Lyophilized 3D Collagen Matrix</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Matriz tridimensional de colágeno liofilizada de poros abiertos (102x102x3mm)</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
+          <t>102 x 102 x 3mm</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>10800</v>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>NEAR SINGLE SOURCE</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
         <is>
           <t>MedSkin Solutions Dr. Suwelack AG</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="G8" s="3" t="inlineStr">
         <is>
           <t>MatriDerm</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>EXACT MATCH</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>matriderm.com</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>Yes (K201577)</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>ONLY product with bovine collagen I, III, AND V in lyophilized 3D open-pore matrix. Used in 70+ countries. CryoSafe processing.</t>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>https://matriderm.com</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>Yes — 510(k) K201577</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>Native bovine collagen I, III, V with elastin hydrolysate. Lyophilized, non-cross-linked, open pore. 170+ publications.</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>ONLY product with I/III/V spec. CryoSafe processing. Used in 70+ countries.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>Lyophilized 3D Open-Pore Collagen Matrix</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr"/>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr"/>
+      <c r="C9" s="2" t="inlineStr"/>
+      <c r="D9" s="2" t="inlineStr"/>
+      <c r="E9" s="2" t="inlineStr"/>
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>Integra LifeSciences</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>Integra Wound Matrix / Bilayer</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>Integra Wound Matrix</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>ALTERNATIVE</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>integralife.com</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>https://integralife.com</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>Bovine collagen + GAG + silicone. Different composition (no types III/V specifically). Market leader in skin substitutes.</t>
+      <c r="L9" s="5" t="inlineStr">
+        <is>
+          <t>Bovine collagen + GAG + silicone bilayer. Market leader in dermal regeneration.</t>
+        </is>
+      </c>
+      <c r="M9" s="5" t="inlineStr">
+        <is>
+          <t>Does NOT specify collagen types I, III, V. Different composition. Would not meet tender spec.</t>
         </is>
       </c>
     </row>
@@ -887,78 +1014,104 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Hidrogel con plata iónica y carboximetilcelulosa (tubo 8oz)</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
+          <t>8oz tube (also 0.25oz, 1.5oz, 3oz)</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>14400</v>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>NEAR SINGLE SOURCE</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
         <is>
           <t>Medline Industries</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="G10" s="3" t="inlineStr">
         <is>
           <t>SilvaSorb Gel</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>USA (IL)</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>medline.com</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>EXACT MATCH</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>USA (Illinois)</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>https://medline.com</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>EXACT MATCH: ionic silver 0.024% + CMC 2.5%. All 4 tube sizes (0.25, 1.5, 3, 8 oz) match tender. Microlattice silver technology.</t>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>Ionic silver 0.024% + CMC 2.5%. All 4 tube sizes match. Microlattice silver technology.</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>3-day antimicrobial barrier. Non-staining. Broad spectrum (MRSA, VRE).</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>Hydrogel with Ionic Silver &amp; CMC</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr"/>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr"/>
+      <c r="C11" s="2" t="inlineStr"/>
+      <c r="D11" s="2" t="inlineStr"/>
+      <c r="E11" s="2" t="inlineStr"/>
+      <c r="F11" s="5" t="inlineStr">
         <is>
           <t>Cardinal Health</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>Hydrogel Ag</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>ALTERNATIVE</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>cardinalhealth.com</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="inlineStr">
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>https://cardinalhealth.com</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="I11" s="3" t="inlineStr">
-        <is>
-          <t>Silver hydrogel alternative, different concentration.</t>
+      <c r="L11" s="5" t="inlineStr">
+        <is>
+          <t>Silver hydrogel wound gel. Different silver concentration.</t>
+        </is>
+      </c>
+      <c r="M11" s="5" t="inlineStr">
+        <is>
+          <t>Silver concentration and CMC percentage differ from 0.024%/2.5% spec.</t>
         </is>
       </c>
     </row>
@@ -966,85 +1119,111 @@
       <c r="A12" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>Hydrogel with Ionic Silver &amp; CMC</t>
-        </is>
-      </c>
+      <c r="B12" s="2" t="inlineStr"/>
       <c r="C12" s="2" t="inlineStr"/>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>Derma Sciences / Integra</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>Silvasorb / MediHoney Ag Gel</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr"/>
+      <c r="E12" s="2" t="inlineStr"/>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>Integra LifeSciences</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>MediHoney Ag Gel</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>ALTERNATIVE</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>integralife.com</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>https://integralife.com</t>
+        </is>
+      </c>
+      <c r="K12" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>Silver-based gel options for wound care.</t>
+      <c r="L12" s="5" t="inlineStr">
+        <is>
+          <t>Honey-based wound gel with silver. Different mechanism.</t>
+        </is>
+      </c>
+      <c r="M12" s="5" t="inlineStr">
+        <is>
+          <t>Manuka honey + silver — completely different base. Would not meet spec.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>Hydrocellular Foam with Silicone (Quadrilobed)</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>Apósito combinado espuma hidrocelular con adhesivo de silicona, cuadrilobular (21.6x23cm)</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Hydrocellular Foam (Quadrilobed)</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>21.6cm x 23cm (range 10.3cm to 25.5cm)</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>34200</v>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>SINGLE SOURCE</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
         <is>
           <t>Smith+Nephew</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="G13" s="3" t="inlineStr">
         <is>
           <t>ALLEVYN Life</t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>EXACT MATCH — SOLE QUADRILOBE</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
         <is>
           <t>UK</t>
         </is>
       </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>smith-nephew.com</t>
-        </is>
-      </c>
-      <c r="H13" s="3" t="inlineStr">
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>https://smith-nephew.com</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="I13" s="3" t="inlineStr">
-        <is>
-          <t>SOLE QUADRILOBE MANUFACTURER. 5-layer construction, visual change indicator, silicone adhesive. All tender sizes match.</t>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>ONLY quadrilobe foam on market. 5-layer construction. Visual change indicator. All tender sizes available.</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>Sole manufacturer of quadrilobe shape. 7-day wear. Hyper-absorber lock-away core.</t>
         </is>
       </c>
     </row>
@@ -1052,81 +1231,97 @@
       <c r="A14" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>Hydrocellular Foam with Silicone (Quadrilobed)</t>
-        </is>
-      </c>
+      <c r="B14" s="2" t="inlineStr"/>
       <c r="C14" s="2" t="inlineStr"/>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>Mölnlycke Health Care</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr"/>
+      <c r="E14" s="2" t="inlineStr"/>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>Molnlycke Health Care</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
         <is>
           <t>Mepilex Border Flex</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>ALTERNATIVE</t>
+        </is>
+      </c>
+      <c r="I14" s="5" t="inlineStr">
         <is>
           <t>Sweden</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>molnlycke.com</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>https://molnlycke.com</t>
+        </is>
+      </c>
+      <c r="K14" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>Flex-cut shape (not quadrilobe). Safetac silicone. Major competitor in foam category.</t>
+      <c r="L14" s="5" t="inlineStr">
+        <is>
+          <t>Flex-cut shape (NOT quadrilobe). Safetac silicone. 5-layer foam.</t>
+        </is>
+      </c>
+      <c r="M14" s="5" t="inlineStr">
+        <is>
+          <t>Flex-cut cross, not quadrilobe. Would NOT meet shape requirement.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
+      <c r="A15" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>Hydrocellular Foam with Silicone (Quadrilobed)</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr"/>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr"/>
+      <c r="C15" s="2" t="inlineStr"/>
+      <c r="D15" s="2" t="inlineStr"/>
+      <c r="E15" s="2" t="inlineStr"/>
+      <c r="F15" s="5" t="inlineStr">
         <is>
           <t>Coloplast</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="G15" s="5" t="inlineStr">
         <is>
           <t>Biatain Silicone</t>
         </is>
       </c>
-      <c r="F15" s="3" t="inlineStr">
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>ALTERNATIVE</t>
+        </is>
+      </c>
+      <c r="I15" s="5" t="inlineStr">
         <is>
           <t>Denmark</t>
         </is>
       </c>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t>coloplast.com</t>
-        </is>
-      </c>
-      <c r="H15" s="3" t="inlineStr">
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>https://coloplast.com</t>
+        </is>
+      </c>
+      <c r="K15" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="I15" s="3" t="inlineStr">
-        <is>
-          <t>Silicone foam dressing, square shape. 3DFit technology.</t>
+      <c r="L15" s="5" t="inlineStr">
+        <is>
+          <t>Square silicone foam with 3DFit Technology.</t>
+        </is>
+      </c>
+      <c r="M15" s="5" t="inlineStr">
+        <is>
+          <t>Standard square shape — NOT quadrilobe. Would NOT meet spec.</t>
         </is>
       </c>
     </row>
@@ -1134,85 +1329,111 @@
       <c r="A16" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>Hydrocellular Foam with Silicone (Quadrilobed)</t>
-        </is>
-      </c>
+      <c r="B16" s="2" t="inlineStr"/>
       <c r="C16" s="2" t="inlineStr"/>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr"/>
+      <c r="E16" s="2" t="inlineStr"/>
+      <c r="F16" s="5" t="inlineStr">
         <is>
           <t>ConvaTec</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="G16" s="5" t="inlineStr">
         <is>
           <t>AQUACEL Foam Pro</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>ALTERNATIVE</t>
+        </is>
+      </c>
+      <c r="I16" s="5" t="inlineStr">
         <is>
           <t>UK/USA</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>convatec.com</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>https://convatec.com</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>Hydrofiber + foam combo with silicone border. Not quadrilobe.</t>
+      <c r="L16" s="5" t="inlineStr">
+        <is>
+          <t>Hydrofiber + foam combo with silicone border.</t>
+        </is>
+      </c>
+      <c r="M16" s="5" t="inlineStr">
+        <is>
+          <t>Standard shape — NOT quadrilobe. Different absorption mechanism (Hydrofiber).</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
+      <c r="A17" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>Acellular Fish Skin Matrix (Cod)</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>Matriz acelular con ácidos grasos y omega 3, fragmentado 4cm²</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Acellular Fish Skin Matrix</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Fragmented 4cm² (also laminated, fenestrated, mesh)</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>18000</v>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>SINGLE SOURCE</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
         <is>
           <t>Kerecis (now Coloplast)</t>
         </is>
       </c>
-      <c r="E17" s="3" t="inlineStr">
+      <c r="G17" s="3" t="inlineStr">
         <is>
           <t>Kerecis Omega3 Wound / MicroGraft / Shield / GraftGuide</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>EXACT MATCH — SOLE MANUFACTURER</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
         <is>
           <t>Iceland / Denmark</t>
         </is>
       </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t>kerecis.com</t>
-        </is>
-      </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>Yes (2013)</t>
-        </is>
-      </c>
-      <c r="I17" s="3" t="inlineStr">
-        <is>
-          <t>SOLE MANUFACTURER worldwide. Only acellular fish skin (Atlantic cod) matrix. Acquired by Coloplast for $1.3B in 2023. All formats (fragmented, laminated, fenestrated, mesh) match tender.</t>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>https://kerecis.com</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>Yes — 510(k) 2013</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>SOLE MANUFACTURER worldwide. All formats: MicroGraft (fragmented), Omega3 Wound (laminated), Shield (fenestrated), GraftGuide (mesh).</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>Only fish skin matrix in existence. Acquired by Coloplast for $1.3B (2023). Only non-mammalian acellular dermal matrix.</t>
         </is>
       </c>
     </row>
@@ -1222,83 +1443,109 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Hydrocolloid Dressing with Regulating Effect</t>
+          <t>Hydrocolloid Dressing</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Apósito hidrocoloide con efecto regulador (15x15cm)</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
+          <t>15cm x 15cm</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>25200</v>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Competitive</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
         <is>
           <t>ConvaTec</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>DuoDERM Signal / Granuflex</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>DuoDERM Signal</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>EXACT MATCH</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
         <is>
           <t>UK/USA</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>convatec.com</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>https://convatec.com</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>Invented hydrocolloid dressings. CGF (Control Gel Formula) technology. Visual change indicator. 15x15cm available.</t>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>Hydrocolloid with visual change indicator. CMC + pectin inner, PU outer. 15x15cm available. Invented hydrocolloid dressings.</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>CGF (Control Gel Formula) technology. First hydrocolloid dressing ever made.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n">
+      <c r="A19" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>Hydrocolloid Dressing with Regulating Effect</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr"/>
-      <c r="D19" s="3" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr"/>
+      <c r="C19" s="2" t="inlineStr"/>
+      <c r="D19" s="2" t="inlineStr"/>
+      <c r="E19" s="2" t="inlineStr"/>
+      <c r="F19" s="4" t="inlineStr">
         <is>
           <t>Coloplast</t>
         </is>
       </c>
-      <c r="E19" s="3" t="inlineStr">
+      <c r="G19" s="4" t="inlineStr">
         <is>
           <t>Comfeel Plus</t>
         </is>
       </c>
-      <c r="F19" s="3" t="inlineStr">
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>CLOSE MATCH</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
         <is>
           <t>Denmark</t>
         </is>
       </c>
-      <c r="G19" s="3" t="inlineStr">
-        <is>
-          <t>coloplast.com</t>
-        </is>
-      </c>
-      <c r="H19" s="3" t="inlineStr">
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>https://coloplast.com</t>
+        </is>
+      </c>
+      <c r="K19" s="4" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="I19" s="3" t="inlineStr">
-        <is>
-          <t>CMC + alginate hydrocolloid. Multiple sizes including 15x15cm.</t>
+      <c r="L19" s="4" t="inlineStr">
+        <is>
+          <t>CMC particles + calcium alginate in adhesive matrix. PU film. 15x15cm available.</t>
+        </is>
+      </c>
+      <c r="M19" s="4" t="inlineStr">
+        <is>
+          <t>Pectin-free, latex-free. Uses calcium alginate instead of pectin.</t>
         </is>
       </c>
     </row>
@@ -1306,86 +1553,102 @@
       <c r="A20" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>Hydrocolloid Dressing with Regulating Effect</t>
-        </is>
-      </c>
+      <c r="B20" s="2" t="inlineStr"/>
       <c r="C20" s="2" t="inlineStr"/>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr"/>
+      <c r="E20" s="2" t="inlineStr"/>
+      <c r="F20" s="4" t="inlineStr">
         <is>
           <t>3M / Solventum</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="G20" s="4" t="inlineStr">
         <is>
           <t>Tegaderm Hydrocolloid</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>CLOSE MATCH</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>solventum.com</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>https://solventum.com</t>
+        </is>
+      </c>
+      <c r="K20" s="4" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>Thin and standard hydrocolloid options.</t>
+      <c r="L20" s="4" t="inlineStr">
+        <is>
+          <t>Long-wearing water-resistant hydrocolloid. Oval, square, sacral, thin variants.</t>
+        </is>
+      </c>
+      <c r="M20" s="4" t="inlineStr">
+        <is>
+          <t>May not have specific regulating/indicator feature.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="n">
+      <c r="A21" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>Hydrocolloid Dressing with Regulating Effect</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr"/>
-      <c r="D21" s="3" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr"/>
+      <c r="C21" s="2" t="inlineStr"/>
+      <c r="D21" s="2" t="inlineStr"/>
+      <c r="E21" s="2" t="inlineStr"/>
+      <c r="F21" s="5" t="inlineStr">
         <is>
           <t>Cardinal Health</t>
         </is>
       </c>
-      <c r="E21" s="3" t="inlineStr">
+      <c r="G21" s="5" t="inlineStr">
         <is>
           <t>Kendall Hydrocolloid</t>
         </is>
       </c>
-      <c r="F21" s="3" t="inlineStr">
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>ALTERNATIVE</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="G21" s="3" t="inlineStr">
-        <is>
-          <t>cardinalhealth.com</t>
-        </is>
-      </c>
-      <c r="H21" s="3" t="inlineStr">
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>https://cardinalhealth.com</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="I21" s="3" t="inlineStr">
-        <is>
-          <t>Cost-effective hydrocolloid alternative.</t>
+      <c r="L21" s="5" t="inlineStr">
+        <is>
+          <t>Kendall alginate hydrocolloid with 30% alginate for absorbency.</t>
+        </is>
+      </c>
+      <c r="M21" s="5" t="inlineStr">
+        <is>
+          <t>Budget product. May not have indicator feature.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I21"/>
+  <autoFilter ref="A1:M21"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1396,52 +1659,64 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Cat #</t>
+          <t>Cat</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Product Category</t>
+          <t>FT Code</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Primary Match (Tender Target)</t>
+          <t>Category</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Manufacturer</t>
+          <t>Spanish Name</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t># of Competitors Found</t>
+          <t>Size Requested</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Single-Source?</t>
+          <t>Qty</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Tender Qty</t>
+          <t>Specifications</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Competitive Status</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Status Detail</t>
         </is>
       </c>
     </row>
@@ -1449,65 +1724,81 @@
       <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Collagen-Alginate Dressing</t>
-        </is>
+      <c r="B2" s="2" t="n">
+        <v>100570</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>FIBRACOL Plus</t>
+          <t>Collagen-Alginate Wound Dressing</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>3M/Solventum</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+          <t>Apósito a base de colágeno y alginato, 10.2cm x 11.1cm (4" x 4⅜")</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>10.2cm x 11.1cm (4" x 4⅜")</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>115200</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>115,200</t>
+          <t>Sterile, non-adherent, soft, conformable. Absorbent/gelling. Moist wound environment. Controls exudate. Structural support for cellular growth. ISO 13485, FDA cleared.</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Competitive</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>5 competitor(s) identified</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="2" t="n">
+        <v>105295</v>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>Nano Hemicellulose Membrane &amp; Gel</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>NanoGen Aktiv + Aktigel</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>Genadyne Biotechnologies</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>YES — Single Source</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>3,600</t>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Sistema de membrana y gel de hemicelulosa de nanoestructura, 8cm x 8cm</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Membrane 8cm x 8cm, Gel 90ml</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>3600</v>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Plant-derived stem cells. Hemicellulose membrane &lt;2nm. Cellular signaling system. Mimics ECM. Includes activating gel. Positively charged at physiological pH. Removes bacteria electrostatically. No silver. 100% natural, biodegradable, nanotechnology.</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>SINGLE SOURCE</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>1 competitor(s) identified</t>
         </is>
       </c>
     </row>
@@ -1515,65 +1806,81 @@
       <c r="A4" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="2" t="n">
+        <v>105362</v>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>Lyophilized 3D Collagen Matrix</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>MatriDerm</t>
-        </is>
-      </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>MedSkin Solutions Dr. Suwelack</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Effectively yes (I, III, V spec)</t>
-        </is>
+          <t>Matriz tridimensional de colágeno liofilizada de poros abiertos, 102 x 102 x 3mm</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>102 x 102 x 3mm</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>10800</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>10,800</t>
+          <t>100% bovine collagen types I, III, V. Conforms to wound bed. Moldable. Hemostatic. Biodegradable. Absorbs 20x weight. Latex-free. Sterile.</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>NEAR SINGLE SOURCE</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>2 competitor(s) identified</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>Hydrogel Ionic Silver + CMC</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>SilvaSorb Gel</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>Medline Industries</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>No (but exact spec match)</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>14,400</t>
+      <c r="B5" s="2" t="n">
+        <v>107365</v>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Hydrogel with Ionic Silver &amp; CMC</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Hidrogel con plata iónica y carboximetilcelulosa, tubo de 8oz</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>8oz tube (also 0.25oz, 1.5oz, 3oz)</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>14400</v>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Ionic silver at 0.024%. 2.5% carboxymethylcellulose. Hydrogel. Tube sizes: 0.25oz, 1.5oz, 3oz, 8oz.</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>NEAR SINGLE SOURCE</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>3 competitor(s) identified</t>
         </is>
       </c>
     </row>
@@ -1581,65 +1888,81 @@
       <c r="A6" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Hydrocellular Foam Quadrilobe</t>
-        </is>
+      <c r="B6" s="2" t="n">
+        <v>108611</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>ALLEVYN Life</t>
+          <t>Hydrocellular Foam (Quadrilobed)</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Smith+Nephew</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t>YES for quadrilobe shape</t>
-        </is>
+          <t>Apósito combinado espuma hidrocelular con adhesivo de silicona, cuadrilobular, 21.6cm x 23cm</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>21.6cm x 23cm (range 10.3cm to 25.5cm)</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>34200</v>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>34,200</t>
+          <t>Hydrocellular foam. Silicone adhesive. Absorbent padded core. Visual change indicator. Repositionable. Quadrilobed shape. Sterile, single use.</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>SINGLE SOURCE</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>4 competitor(s) identified</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="2" t="n">
+        <v>109014</v>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>Acellular Fish Skin Matrix</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>Kerecis Omega3</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>Kerecis / Coloplast</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>YES — Sole worldwide</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>18,000</t>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Matriz acelular con ácidos grasos y omega 3, fragmentado 4cm²</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Fragmented 4cm² (also laminated, fenestrated, mesh)</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>18000</v>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>Atlantic cod (Gadus morhua) skin. Fatty acids, omega-3, collagen. 3D structure. Elastic. Fragmented, laminated, fenestrated, mesh formats. Sterile, single-use, biodegradable.</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>SINGLE SOURCE</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>1 competitor(s) identified</t>
         </is>
       </c>
     </row>
@@ -1647,37 +1970,44 @@
       <c r="A8" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>Hydrocolloid w/ Regulating Effect</t>
-        </is>
+      <c r="B8" s="2" t="n">
+        <v>109011</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>DuoDERM Signal</t>
+          <t>Hydrocolloid Dressing</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>ConvaTec</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+          <t>Apósito hidrocoloide con efecto regulador, 15cm x 15cm</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>15cm x 15cm</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>25200</v>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>25,200</t>
+          <t>Single-layer. Powdered components absorb/regulate fluids. Semi-permeable polyurethane outer. Hydrocolloid contact layer (CMC, pectin, cellulose). Absorbent, breathable.</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Competitive</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>4 competitor(s) identified</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1688,140 +2018,862 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="90" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t>Wound Care Competitive Analysis — Key Insights</t>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>FDA Cleared</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Products</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Categories They Compete In</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="inlineStr"/>
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>3M / Solventum</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>https://solventum.com</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>Yes — 510(k) K982597</t>
+        </is>
+      </c>
+      <c r="E2" s="6" t="inlineStr">
+        <is>
+          <t>FIBRACOL Plus; Tegaderm Hydrocolloid</t>
+        </is>
+      </c>
+      <c r="F2" s="6" t="inlineStr">
+        <is>
+          <t>Collagen-Alginate Wound Dressing; Hydrocolloid Dressing</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="inlineStr">
-        <is>
-          <t>SINGLE-SOURCE PRODUCTS (specs written around one manufacturer):</t>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Human BioSciences</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>https://humanbiosciences.com</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Medifil II</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Collagen-Alginate Wound Dressing</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>• Cat 2 — NanoGen (Genadyne): Only nano-hemicellulose membrane + gel system in market</t>
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Safe n' Simple</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>https://sns-medical.com</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>Simpurity Collagen Pad</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>Collagen-Alginate Wound Dressing</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>• Cat 5 — ALLEVYN Life (Smith+Nephew): Only quadrilobe-shaped foam dressing</t>
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>DermaRite Industries</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>https://dermarite.com</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>DermaCol/Ag</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Collagen-Alginate Wound Dressing</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>• Cat 6 — Kerecis Omega3 (Coloplast): Only fish skin matrix worldwide</t>
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Foryou Medical (LUOFUCON)</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>https://en.foryoumedical.com</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>Yes — 510(k)</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>Collagen Wound Dressing</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>Collagen-Alginate Wound Dressing</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr"/>
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Genadyne Biotechnologies</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>https://genadyne.com</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>USA (New York)</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>NanoGen Aktiv + NanoGen Aktigel</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Nano Hemicellulose Membrane &amp; Gel</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>NEAR SINGLE-SOURCE:</t>
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>MedSkin Solutions Dr. Suwelack AG</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>https://matriderm.com</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>Yes — 510(k) K201577</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>MatriDerm</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>Lyophilized 3D Collagen Matrix</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>• Cat 3 — MatriDerm: Only collagen matrix with types I, III, AND V specifically</t>
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Integra LifeSciences</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>https://integralife.com</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Integra Wound Matrix; MediHoney Ag Gel</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Lyophilized 3D Collagen Matrix; Hydrogel with Ionic Silver &amp; CMC</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>• Cat 4 — SilvaSorb: Exact ionic silver % + CMC % + all 4 tube sizes match</t>
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>Medline Industries</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>https://medline.com</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>USA (Illinois)</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>SilvaSorb Gel</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>Hydrogel with Ionic Silver &amp; CMC</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="inlineStr"/>
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Cardinal Health</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>https://cardinalhealth.com</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Hydrogel Ag; Kendall Hydrocolloid</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Hydrogel with Ionic Silver &amp; CMC; Hydrocolloid Dressing</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t>COMPETITIVE CATEGORIES (multiple viable alternatives):</t>
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Smith+Nephew</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>https://smith-nephew.com</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>ALLEVYN Life</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>Hydrocellular Foam (Quadrilobed)</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>• Cat 1 — Collagen-Alginate: 5+ manufacturers (3M, HBS, Safe n' Simple, DermaRite, Foryou)</t>
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Molnlycke Health Care</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>https://molnlycke.com</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Mepilex Border Flex</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Hydrocellular Foam (Quadrilobed)</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>• Cat 7 — Hydrocolloid: 4+ manufacturers (ConvaTec, Coloplast, 3M, Cardinal Health)</t>
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Coloplast</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>https://coloplast.com</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>Denmark</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>Biatain Silicone; Comfeel Plus</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>Hydrocellular Foam (Quadrilobed); Hydrocolloid Dressing</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="7" t="inlineStr"/>
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>ConvaTec</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>https://convatec.com</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>UK/USA</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>AQUACEL Foam Pro; DuoDERM Signal</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Hydrocellular Foam (Quadrilobed); Hydrocolloid Dressing</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="inlineStr">
-        <is>
-          <t>TENDER CONTEXT:</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>• This appears to be a Latin American government procurement tender (likely Panama based on IEA reference)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>• Total quantities suggest a national health system contract</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>• Specs for categories 2, 5, and 6 are highly specific — likely designed for a preferred vendor</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>• Categories 1 and 7 have the most room for competitive bidding</t>
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>Kerecis (now Coloplast)</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>https://kerecis.com</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>Iceland / Denmark</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>Yes — 510(k) 2013</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>Kerecis Omega3 Wound / MicroGraft / Shield / GraftGuide</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>Acellular Fish Skin Matrix</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
-  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Cat</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Product Category</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Primary Match</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Manufacturer</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Match Type</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t># Competitors</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Competitive Status</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Tender Qty</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Collagen-Alginate Wound Dressing</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>FIBRACOL Plus</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>3M / Solventum</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>EXACT MATCH</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Competitive</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>115,200</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Nano Hemicellulose Membrane &amp; Gel</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>NanoGen Aktiv + NanoGen Aktigel</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Genadyne Biotechnologies</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>EXACT MATCH — SOLE MANUFACTURER</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" s="7" t="inlineStr">
+        <is>
+          <t>SINGLE SOURCE</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Lyophilized 3D Collagen Matrix</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>MatriDerm</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>MedSkin Solutions Dr. Suwelack AG</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>EXACT MATCH</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G4" s="7" t="inlineStr">
+        <is>
+          <t>NEAR SINGLE SOURCE</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>10,800</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Hydrogel with Ionic Silver &amp; CMC</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>SilvaSorb Gel</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Medline Industries</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>EXACT MATCH</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>NEAR SINGLE SOURCE</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>14,400</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Hydrocellular Foam (Quadrilobed)</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>ALLEVYN Life</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Smith+Nephew</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>EXACT MATCH — SOLE QUADRILOBE</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>SINGLE SOURCE</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>34,200</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Acellular Fish Skin Matrix</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Kerecis Omega3 Wound / MicroGraft / Shield / GraftGuide</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Kerecis (now Coloplast)</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>EXACT MATCH — SOLE MANUFACTURER</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>SINGLE SOURCE</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>18,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Hydrocolloid Dressing</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>DuoDERM Signal</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>ConvaTec</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>EXACT MATCH</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Competitive</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>25,200</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>